--- a/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>TSBX</t>
   </si>
@@ -1140,8 +1140,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-17400</v>
       </c>
       <c r="E23" s="3">
         <v>-21500</v>
@@ -1236,8 +1236,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-17300</v>
       </c>
       <c r="E26" s="3">
         <v>-21500</v>
@@ -1268,8 +1268,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-17300</v>
       </c>
       <c r="E27" s="3">
         <v>-21500</v>
@@ -1460,8 +1460,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-17300</v>
       </c>
       <c r="E33" s="3">
         <v>-21500</v>
@@ -1524,8 +1524,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-17300</v>
       </c>
       <c r="E35" s="3">
         <v>-21500</v>
@@ -2258,7 +2258,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E62" s="3">
         <v>4700</v>
@@ -2385,8 +2385,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>17400</v>
       </c>
       <c r="E66" s="3">
         <v>23400</v>
@@ -2559,8 +2559,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-160300</v>
       </c>
       <c r="E72" s="3">
         <v>-143000</v>
@@ -2687,8 +2687,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>113900</v>
       </c>
       <c r="E76" s="3">
         <v>-120600</v>
@@ -2788,8 +2788,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-17300</v>
       </c>
       <c r="E81" s="3">
         <v>-21500</v>
@@ -3026,8 +3026,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-18800</v>
       </c>
       <c r="E89" s="3">
         <v>-14700</v>
@@ -3073,16 +3073,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3168,8 +3168,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-42300</v>
       </c>
       <c r="E94" s="3">
         <v>3000</v>

--- a/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>TSBX</t>
   </si>
@@ -656,64 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -724,28 +731,34 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>19300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>73300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>10700</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -776,8 +789,14 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -808,8 +827,14 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,40 +847,48 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F12" s="3">
         <v>14200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>17200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>15700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>86700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>18700</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -886,8 +919,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -918,8 +957,14 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -950,8 +995,14 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -961,40 +1012,48 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F17" s="3">
         <v>18900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>21900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>19700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>104900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>23400</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1002,31 +1061,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-21900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-31600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-12700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1039,8 +1104,10 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1048,31 +1115,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1080,31 +1153,37 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-20800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-26800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-11900</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1135,40 +1214,52 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-17400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-21500</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-30700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-12600</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1176,22 +1267,22 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1199,8 +1290,14 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1231,72 +1328,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-17300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-21500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-30800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-12600</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-17300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-21500</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-31000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-12700</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1327,8 +1442,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1359,8 +1480,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1391,8 +1518,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1423,8 +1556,14 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1432,63 +1571,75 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-17300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-21500</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-31000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-12700</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1519,77 +1670,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-17300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-21500</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-31000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-12700</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1602,8 +1771,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1616,26 +1787,28 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F41" s="3">
         <v>38800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>21500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>33500</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1648,26 +1821,32 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>77000</v>
+      </c>
+      <c r="F42" s="3">
         <v>70300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>27700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>30500</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1680,26 +1859,32 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1897,14 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1744,26 +1935,32 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F45" s="3">
         <v>9500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,26 +1973,32 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>102600</v>
+      </c>
+      <c r="F46" s="3">
         <v>118800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>56100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>75400</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,8 +2011,14 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1840,26 +2049,32 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F48" s="3">
         <v>11300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +2087,14 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1904,8 +2125,14 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1936,8 +2163,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1968,26 +2201,32 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2800</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2000,8 +2239,14 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2032,26 +2277,32 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>112800</v>
+      </c>
+      <c r="F54" s="3">
         <v>131300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>74800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>92300</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2064,8 +2315,14 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2078,8 +2335,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2092,26 +2351,28 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,8 +2385,14 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2156,26 +2423,32 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F59" s="3">
         <v>10700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>18500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>14600</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,26 +2461,32 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F60" s="3">
         <v>13100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>18700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15400</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2220,8 +2499,14 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2252,26 +2537,32 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F62" s="3">
         <v>4300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,8 +2575,14 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2316,8 +2613,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,8 +2651,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2380,26 +2689,32 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F66" s="3">
         <v>17400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>20500</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2412,8 +2727,14 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2426,8 +2747,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2458,8 +2781,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2490,8 +2819,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2499,17 +2834,17 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
         <v>172000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>172000</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2522,8 +2857,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2554,26 +2895,32 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-196400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-176800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-160300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-143000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-121500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2586,8 +2933,14 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2618,8 +2971,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2650,8 +3009,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2682,26 +3047,32 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>98700</v>
+      </c>
+      <c r="F76" s="3">
         <v>113900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-120600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-100200</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2714,8 +3085,14 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2746,77 +3123,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-17300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-21500</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-31000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-12700</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2829,13 +3224,15 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
@@ -2844,16 +3241,16 @@
         <v>700</v>
       </c>
       <c r="G83" s="3">
-        <v>3900</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>700</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2861,8 +3258,14 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2893,8 +3296,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2925,8 +3334,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2957,8 +3372,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2989,8 +3410,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3021,40 +3448,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-18800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-17200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-71100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-16500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3067,29 +3506,31 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4600</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -3099,8 +3540,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3131,8 +3578,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3163,40 +3616,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-42300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>16500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-14900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3209,8 +3674,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3241,8 +3708,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3273,8 +3746,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3305,8 +3784,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3337,31 +3822,37 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
         <v>78300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3369,8 +3860,14 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3401,36 +3898,48 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="F102" s="3">
         <v>17200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-88700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-17200</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>TSBX</t>
   </si>
@@ -656,60 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -719,8 +720,11 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -737,17 +741,17 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>19300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>73300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10700</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -757,8 +761,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,8 +802,11 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -833,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,35 +862,36 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E12" s="3">
         <v>15800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>86700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18700</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +942,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +983,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1001,8 +1024,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,35 +1040,36 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E17" s="3">
         <v>20700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>104900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1052,8 +1079,11 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1061,26 +1091,26 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-17900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-21900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-31600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1120,11 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1139,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1115,26 +1149,26 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,8 +1178,11 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1153,26 +1190,26 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-16000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1182,8 +1219,11 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1220,35 +1260,38 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21500</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-30700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,8 +1301,11 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1267,25 +1313,25 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1296,8 +1342,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,35 +1383,38 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1372,35 +1424,38 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21500</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-31000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1410,8 +1465,11 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1629,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1571,26 +1641,26 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1600,35 +1670,38 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21500</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-31000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1638,8 +1711,11 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,35 +1752,38 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21500</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-31000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,40 +1793,43 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1757,8 +1839,11 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,29 +1875,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E41" s="3">
         <v>14400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33500</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,29 +1914,32 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E42" s="3">
         <v>63400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>77000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>70300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30500</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,8 +1955,11 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1874,20 +1967,20 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,8 +1996,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1941,29 +2037,32 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1979,29 +2078,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E46" s="3">
         <v>85000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>102600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>118800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>56100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2119,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2055,29 +2160,32 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2201,11 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2131,8 +2242,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,8 +2324,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2219,17 +2339,17 @@
         <v>1100</v>
       </c>
       <c r="F52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2800</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2245,8 +2365,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,29 +2406,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E54" s="3">
         <v>94400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>112800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>131300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2447,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,29 +2483,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,8 +2522,11 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2429,29 +2563,32 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E59" s="3">
         <v>11200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,29 +2604,32 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E60" s="3">
         <v>12600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2645,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2543,29 +2686,32 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,8 +2727,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,29 +2850,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E66" s="3">
         <v>14400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20500</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +2891,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2840,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>172000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>172000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2863,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,29 +3072,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-217700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-196400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-176800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-160300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-143000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-121500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,8 +3113,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,29 +3236,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E76" s="3">
         <v>80000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>98700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>113900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-120600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-100200</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3277,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,40 +3318,43 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3172,35 +3364,38 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21500</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-31000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3210,8 +3405,11 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,8 +3424,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3235,7 +3434,7 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -3247,14 +3446,14 @@
         <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,8 +3463,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,35 +3668,38 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-71100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-16500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3492,8 +3709,11 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,8 +3728,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3517,23 +3738,23 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4600</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -3546,8 +3767,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,35 +3849,38 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E94" s="3">
         <v>14100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>16500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,8 +3890,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +3909,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +3948,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,8 +4071,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3837,25 +4083,25 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>78300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
@@ -3866,8 +4112,11 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3904,35 +4153,38 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-88700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3940,6 +4192,9 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>TSBX</t>
   </si>
@@ -656,64 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,38 +724,41 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>19300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>73300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -764,31 +768,34 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>13300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>15100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -805,31 +812,34 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4300</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -846,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,38 +876,39 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>17700</v>
+        <v>14400</v>
       </c>
       <c r="E12" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F12" s="3">
         <v>15800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14200</v>
       </c>
-      <c r="H12" s="3">
-        <v>17200</v>
-      </c>
       <c r="I12" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J12" s="3">
         <v>15700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>86700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18700</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,31 +962,34 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -986,31 +1006,34 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1027,8 +1050,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,38 +1067,39 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E17" s="3">
         <v>22100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>20700</v>
       </c>
-      <c r="F17" s="3">
-        <v>17900</v>
-      </c>
       <c r="G17" s="3">
+        <v>17700</v>
+      </c>
+      <c r="H17" s="3">
         <v>18900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21900</v>
       </c>
-      <c r="I17" s="3">
-        <v>19700</v>
-      </c>
       <c r="J17" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K17" s="3">
         <v>104900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1082,38 +1109,41 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-18400</v>
       </c>
       <c r="E18" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-20700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-17900</v>
-      </c>
       <c r="G18" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-18900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-21900</v>
       </c>
-      <c r="I18" s="3">
-        <v>-400</v>
-      </c>
       <c r="J18" s="3">
+        <v>200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-31600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1123,8 +1153,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,38 +1173,39 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
-        <v>1100</v>
+        <v>-800</v>
       </c>
       <c r="F20" s="3">
-        <v>1200</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="3">
-        <v>1600</v>
+        <v>-1200</v>
       </c>
       <c r="H20" s="3">
-        <v>300</v>
+        <v>-1600</v>
       </c>
       <c r="I20" s="3">
-        <v>400</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1181,38 +1215,41 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-17400</v>
       </c>
       <c r="E21" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-19100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-16000</v>
-      </c>
       <c r="G21" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-16700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20800</v>
       </c>
-      <c r="I21" s="3">
-        <v>700</v>
-      </c>
       <c r="J21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-26800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,31 +1259,34 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1263,38 +1303,41 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21500</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-30700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,37 +1347,40 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1345,8 +1391,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,38 +1435,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,38 +1479,41 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21500</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-31000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,8 +1523,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,38 +1699,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>500</v>
       </c>
       <c r="E32" s="3">
-        <v>-1100</v>
+        <v>800</v>
       </c>
       <c r="F32" s="3">
-        <v>-1200</v>
+        <v>1100</v>
       </c>
       <c r="G32" s="3">
-        <v>-1600</v>
+        <v>1200</v>
       </c>
       <c r="H32" s="3">
-        <v>-300</v>
+        <v>1600</v>
       </c>
       <c r="I32" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,38 +1743,41 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21500</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
+        <v>100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-31000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1787,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,38 +1831,41 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21500</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
+        <v>100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-31000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1796,43 +1875,46 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1842,8 +1924,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,32 +1962,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E41" s="3">
         <v>17400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,32 +2004,35 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E42" s="3">
         <v>45000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>63400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>70300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30500</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1958,32 +2048,35 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
+        <v>200</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,31 +2092,34 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2040,28 +2136,31 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="E45" s="3">
-        <v>7100</v>
+        <v>2300</v>
       </c>
       <c r="F45" s="3">
-        <v>7600</v>
+        <v>2500</v>
       </c>
       <c r="G45" s="3">
-        <v>9500</v>
+        <v>2800</v>
       </c>
       <c r="H45" s="3">
-        <v>6600</v>
+        <v>2600</v>
       </c>
       <c r="I45" s="3">
-        <v>7000</v>
+        <v>2100</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2081,32 +2180,35 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E46" s="3">
         <v>68400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>118800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75400</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,31 +2224,34 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2163,32 +2268,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E48" s="3">
         <v>7400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,8 +2312,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2245,8 +2356,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,13 +2444,16 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
         <v>1100</v>
@@ -2342,17 +2462,17 @@
         <v>1100</v>
       </c>
       <c r="G52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,8 +2488,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,32 +2532,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E54" s="3">
         <v>76900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>94400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>112800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>131300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>92300</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,8 +2576,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,32 +2614,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,31 +2656,34 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2566,31 +2700,34 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>14100</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>11200</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>11900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>10700</v>
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
-        <v>18500</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>14600</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>2300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2200</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2607,32 +2744,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E60" s="3">
         <v>15600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,31 +2788,34 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2689,31 +2832,34 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="E62" s="3">
-        <v>1700</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
-        <v>4300</v>
+        <v>1000</v>
       </c>
       <c r="H62" s="3">
-        <v>4700</v>
+        <v>2600</v>
       </c>
       <c r="I62" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>2500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2400</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2730,8 +2876,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,32 +3008,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E66" s="3">
         <v>17100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20500</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,8 +3052,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3011,13 +3179,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>172000</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>172000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3034,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,32 +3246,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-234700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-217700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-196400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-176800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-160300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-143000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-121500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,8 +3290,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,32 +3422,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E76" s="3">
         <v>59700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>98700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>113900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-120600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-100200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3280,8 +3466,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,43 +3510,46 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3367,38 +3559,41 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21500</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
+        <v>100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-31000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3408,8 +3603,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,38 +3623,39 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
       </c>
       <c r="G83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>900</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
-        <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3665,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,38 +3885,41 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-71100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16500</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3929,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,35 +3949,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4600</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3770,8 +3991,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,38 +4079,41 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>18900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>16500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3893,8 +4123,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,31 +4143,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3951,8 +4185,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,37 +4317,40 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>78300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4115,31 +4361,34 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4156,38 +4405,41 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-88700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4195,6 +4447,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSBX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>TSBX</t>
   </si>
@@ -656,79 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -741,68 +748,74 @@
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>19300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>73300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F9" s="3">
         <v>14400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
-        <v>15800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>13300</v>
-      </c>
       <c r="H9" s="3">
+        <v>700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J9" s="3">
         <v>14200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>15100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,38 +828,44 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F10" s="3">
         <v>-14400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-600</v>
       </c>
-      <c r="F10" s="3">
-        <v>-15800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-13300</v>
-      </c>
       <c r="H10" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="J10" s="3">
         <v>-14200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -859,8 +878,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,52 +902,60 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F12" s="3">
         <v>14400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>17100</v>
       </c>
-      <c r="F12" s="3">
-        <v>15800</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I12" s="3">
         <v>13500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>14200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>16700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>15700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>86700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>18700</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,38 +998,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>-900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1009,25 +1048,31 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
@@ -1036,10 +1081,10 @@
         <v>700</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1053,8 +1098,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1119,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F17" s="3">
         <v>18400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>22100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>20700</v>
       </c>
-      <c r="G17" s="3">
-        <v>17700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J17" s="3">
         <v>18900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>21900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>19100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>104900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>23400</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-18400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-22100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-20700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-18900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-21900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-31600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-12700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,96 +1239,110 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-17400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-20800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-19100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-15800</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-16700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-20800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-26800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-11900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1288,11 +1367,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1306,87 +1385,99 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-17800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-21300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-19600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-16600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-17400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-21500</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-30700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-12600</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1394,8 +1485,14 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1535,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-17000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-21300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-19600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-16500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-17300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-21500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-30800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-12600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-17000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-21300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-19600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-16500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-17300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-21500</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-12700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1685,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1735,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1785,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1835,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-17000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-21300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-19600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-16500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-17300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-21500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-31000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-12700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1985,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-17000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-21300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-19600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-16500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-17300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-21500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-31000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-12700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2114,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,38 +2134,40 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F41" s="3">
         <v>24100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>17400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>14400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>17800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>38800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>33500</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,38 +2180,44 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>21200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>45000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>63400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>77000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>70300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>27700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>30500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2051,8 +2230,14 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2065,24 +2250,24 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2280,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2121,11 +2312,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2139,35 +2330,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,38 +2380,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>34200</v>
+      </c>
+      <c r="F46" s="3">
         <v>51100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>68400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>85000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>102600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>118800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>56100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>75400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,8 +2430,14 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2253,11 +2462,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2271,38 +2480,44 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F48" s="3">
         <v>6500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>11300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2315,8 +2530,14 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2359,8 +2580,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2630,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,38 +2680,44 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>800</v>
+      </c>
+      <c r="F52" s="3">
         <v>900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1100</v>
       </c>
       <c r="G52" s="3">
         <v>1100</v>
       </c>
       <c r="H52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2730,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,38 +2780,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>40100</v>
+      </c>
+      <c r="F54" s="3">
         <v>58500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>76900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>94400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>112800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>131300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>74800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>92300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2830,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2854,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,38 +2874,40 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,22 +2920,28 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2000</v>
       </c>
       <c r="H58" s="3">
         <v>2000</v>
@@ -2686,10 +2953,10 @@
         <v>2000</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2703,38 +2970,44 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,38 +3020,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F60" s="3">
         <v>13600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>12000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15400</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,38 +3070,44 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2835,38 +3120,44 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3170,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3220,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3270,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,38 +3320,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F66" s="3">
         <v>14800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>17400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>23400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3370,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3394,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3440,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3490,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3182,17 +3517,17 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>172000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>172000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3205,8 +3540,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,38 +3590,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-259400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-247600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-234700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-217700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-196400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-176800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-160300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-143000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-121500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3640,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3690,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3740,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,38 +3790,44 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F76" s="3">
         <v>43600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>59700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>80000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>98700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>113900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-120600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-100200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3840,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3890,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-17000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-21300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-19600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-16500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-17300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-21500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-31000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-12700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,13 +4019,15 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
@@ -3639,28 +4036,28 @@
         <v>700</v>
       </c>
       <c r="G83" s="3">
+        <v>700</v>
+      </c>
+      <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3900</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N83" s="3">
+        <v>700</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -3668,8 +4065,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +4115,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +4165,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4215,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4265,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4315,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-17600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-15900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-17500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-15500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-18800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-17200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-71100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-16500</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,41 +4389,43 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4600</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -3994,8 +4435,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4485,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,52 +4535,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F94" s="3">
         <v>24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>18900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>14100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-5300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-42300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>16500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4609,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4170,11 +4637,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4188,8 +4655,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4705,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4755,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,43 +4805,49 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>78300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4364,8 +4855,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4390,11 +4887,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4408,48 +4905,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F102" s="3">
         <v>6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-21000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>17200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-12000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-88700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-17200</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
